--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.69791666666</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,265 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.83333333334</v>
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45960.69791666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G43" t="n">

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK47"/>
+  <dimension ref="A1:AK50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="33">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,126 +6433,513 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45960.66666666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="L50" t="n">
         <v>3.95</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M50" t="n">
         <v>3.35</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N50" t="n">
         <v>2</v>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="Z50" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="n">
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
         <v>45960.69791666666</v>
       </c>
     </row>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK50"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45960.46180555555</v>
+        <v>45960.45833333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45960.47916666666</v>
+        <v>45960.46180555555</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.47916666666</v>
       </c>
     </row>
     <row r="23">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,14 +5958,14 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="M43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N43" t="n">
         <v>2.95</v>
       </c>
-      <c r="N43" t="n">
-        <v>2.25</v>
-      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
@@ -5991,16 +5991,16 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,393 +6553,6 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45960.66666666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Switzerland Super League</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Young Boys</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Switzerland Super League</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Lugano</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Luzern</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Pisa</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" s="3" t="n">
         <v>45960.69791666666</v>
       </c>
     </row>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.37</v>
+        <v>5.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.85</v>
+        <v>4.15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="M45" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.85</v>
+        <v>4.15</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK47"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45960.45833333334</v>
+        <v>45960.4375</v>
       </c>
     </row>
     <row r="13">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45960.46180555555</v>
+        <v>45960.45833333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45960.47916666666</v>
+        <v>45960.46180555555</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.47916666666</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="27">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="30">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.29</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.37</v>
+        <v>5.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="39">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6433,126 +6433,255 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="L48" t="n">
         <v>3.95</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M48" t="n">
         <v>3.35</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N48" t="n">
         <v>2</v>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="Z48" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="n">
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
         <v>45960.69791666666</v>
       </c>
     </row>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G43" t="n">

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N32" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.37</v>
+        <v>6.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M35" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N35" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="M36" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>2.37</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N34" t="n">
         <v>5.1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="N35" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.37</v>
+        <v>5.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.37</v>
+        <v>5.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="N34" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.4</v>
+        <v>2.29</v>
       </c>
       <c r="M35" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>6.7</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N36" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="M48" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.37</v>
+        <v>6.7</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N33" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>2.29</v>
       </c>
       <c r="M34" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>6.7</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N32" t="n">
         <v>5.1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>6.7</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.29</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>6.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.49</v>
+        <v>2.7</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>5.4</v>
+        <v>2.37</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5475,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.57291666666</v>
       </c>
     </row>
     <row r="40">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,10 +5733,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.95</v>
+        <v>2.29</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.15</v>
+        <v>1.83</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,127 +6562,772 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45960.66666666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="L51" t="n">
         <v>3.86</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M51" t="n">
         <v>3.23</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N51" t="n">
         <v>1.99</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="Z51" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="n">
         <v>45960.69791666666</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CS Marítimo</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>União de Leiria</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3" t="n">
+        <v>45960.71875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Leixões</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>45960.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>5.4</v>
+        <v>2.37</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N35" t="n">
-        <v>2.75</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.37</v>
+        <v>5.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,10 +5733,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="O46" t="n">
         <v>3.62</v>
@@ -6384,10 +6384,10 @@
         <v>3.42</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AA46" t="n">
         <v>3.04</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O47" t="n">
         <v>2.34</v>
@@ -6513,10 +6513,10 @@
         <v>3.14</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AA47" t="n">
         <v>3.14</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N49" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.85</v>
+        <v>4.15</v>
       </c>
       <c r="M50" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="O52" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="P52" t="n">
         <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.84</v>
+        <v>3.44</v>
       </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="T52" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U52" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W52" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="X52" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>1.31</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N53" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O53" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="P53" t="n">
         <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.44</v>
+        <v>3.84</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S53" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="T53" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="U53" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V53" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="X53" t="n">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>1.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.37</v>
+        <v>6.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>2.29</v>
       </c>
       <c r="M34" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>6.7</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4935,40 +4935,40 @@
         <v>5.1</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA35" t="n">
         <v>2.05</v>
@@ -4977,10 +4977,10 @@
         <v>1.77</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5580,13 +5580,13 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5595,37 +5595,37 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="M42" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>3.27</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="X42" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>2.15</v>
+        <v>4.4</v>
       </c>
       <c r="O46" t="n">
-        <v>3.62</v>
+        <v>2.34</v>
       </c>
       <c r="P46" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>5.03</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T46" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X46" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,77 +6474,77 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="O47" t="n">
-        <v>2.34</v>
+        <v>3.62</v>
       </c>
       <c r="P47" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.03</v>
+        <v>2.9</v>
       </c>
       <c r="R47" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S47" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="U47" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V47" t="n">
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
         <v>1.27</v>
       </c>
-      <c r="X47" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH47" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45960.39583333334</v>
+        <v>45960.40625</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45960.40625</v>
+        <v>45960.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45960.41666666666</v>
+        <v>45960.42708333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45960.42708333334</v>
+        <v>45960.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45960.4375</v>
+        <v>45960.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45960.45833333334</v>
+        <v>45960.46180555555</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45960.46180555555</v>
+        <v>45960.47916666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45960.47916666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="24">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="27">
@@ -3906,28 +3906,28 @@
         <v>3.46</v>
       </c>
       <c r="P27" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R27" t="n">
         <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="T27" t="n">
         <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
         <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
         <v>4.1</v>
@@ -3939,16 +3939,16 @@
         <v>2.16</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
         <v>1.51</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="30">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.37</v>
+        <v>6.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="35">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.57291666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5079,37 +5079,37 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5451,52 +5451,52 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45960.57291666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="O40" t="n">
-        <v>4.9</v>
+        <v>1.76</v>
       </c>
       <c r="P40" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.89</v>
+        <v>7.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T40" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.12</v>
       </c>
-      <c r="X40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.45</v>
+        <v>2.46</v>
       </c>
       <c r="M41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X41" t="n">
         <v>2.95</v>
       </c>
-      <c r="N41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O41" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Y41" t="n">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AA41" t="n">
-        <v>5.12</v>
+        <v>3.68</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,78 +5829,78 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.27</v>
+        <v>2.15</v>
       </c>
       <c r="O42" t="n">
-        <v>2.46</v>
+        <v>3.64</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.72</v>
+        <v>3.01</v>
       </c>
       <c r="R42" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="T42" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="X42" t="n">
-        <v>6.3</v>
+        <v>3.37</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>3.35</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.81</v>
+        <v>1.28</v>
       </c>
       <c r="AC42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.34</v>
       </c>
-      <c r="AD42" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI42" t="n">
         <v>0</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.24</v>
+        <v>4.92</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T43" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="U43" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="X43" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="M46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N46" t="n">
         <v>3.6</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X46" t="n">
         <v>4.4</v>
       </c>
-      <c r="O46" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X46" t="n">
-        <v>3.14</v>
-      </c>
       <c r="Y46" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.15</v>
+        <v>3.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N47" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="O47" t="n">
-        <v>3.62</v>
+        <v>4.65</v>
       </c>
       <c r="P47" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.35</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W47" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="X47" t="n">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.04</v>
+        <v>3.74</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.69791666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.71875</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="M49" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>3.95</v>
+        <v>2.85</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,522 +6811,6 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Switzerland Super League</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Young Boys</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Pisa</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="3" t="n">
-        <v>45960.69791666666</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Leixões</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" s="3" t="n">
-        <v>45960.71875</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>CS Marítimo</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>União de Leiria</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O53" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X53" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="3" t="n">
         <v>45960.71875</v>
       </c>
     </row>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45960.42708333334</v>
+        <v>45960.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45960.4375</v>
+        <v>45960.42708333334</v>
       </c>
     </row>
     <row r="10">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45960.45833333334</v>
+        <v>45960.4375</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="N27" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="O27" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="R27" t="n">
         <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
         <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
         <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="Y27" t="n">
         <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
         <v>2.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4419,16 +4419,16 @@
         <v>5.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
         <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
         <v>3.75</v>
@@ -4443,7 +4443,7 @@
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
         <v>5.35</v>
@@ -4464,7 +4464,7 @@
         <v>1.44</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4548,16 +4548,16 @@
         <v>6.7</v>
       </c>
       <c r="O32" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="P32" t="n">
         <v>2.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.63</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
         <v>3.85</v>
@@ -4566,22 +4566,22 @@
         <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="Y32" t="n">
         <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AA32" t="n">
         <v>2.05</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O36" t="n">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="U36" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="X36" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z36" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AA36" t="n">
-        <v>2.06</v>
+        <v>5.29</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.59</v>
+        <v>1.94</v>
       </c>
       <c r="M37" t="n">
-        <v>2.79</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.07</v>
+        <v>3.27</v>
       </c>
       <c r="O37" t="n">
-        <v>4.65</v>
+        <v>2.46</v>
       </c>
       <c r="P37" t="n">
-        <v>1.82</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.03</v>
+        <v>3.74</v>
       </c>
       <c r="R37" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>2.23</v>
+        <v>4.1</v>
       </c>
       <c r="T37" t="n">
-        <v>3.54</v>
+        <v>2.04</v>
       </c>
       <c r="U37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.22</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.46</v>
+        <v>4.9</v>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.72</v>
+        <v>1.89</v>
       </c>
       <c r="R38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="U38" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X38" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.99</v>
+        <v>2.28</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.75</v>
+        <v>1.12</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O39" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="P39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X39" t="n">
-        <v>3.77</v>
+        <v>5.75</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.23</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.76</v>
+        <v>4.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S40" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U40" t="n">
         <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X40" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5712,31 +5712,31 @@
         <v>3.05</v>
       </c>
       <c r="P41" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>3.24</v>
       </c>
       <c r="R41" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S41" t="n">
         <v>2.62</v>
       </c>
       <c r="T41" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
         <v>1.36</v>
       </c>
       <c r="V41" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X41" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="Y41" t="n">
         <v>2.1</v>
@@ -5751,10 +5751,10 @@
         <v>1.23</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>4.03</v>
       </c>
       <c r="O42" t="n">
-        <v>3.64</v>
+        <v>2.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.01</v>
+        <v>4.92</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="X42" t="n">
-        <v>3.37</v>
+        <v>3.14</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="O43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.4</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.92</v>
-      </c>
       <c r="U43" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X43" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6225,37 +6225,37 @@
         <v>1.73</v>
       </c>
       <c r="O45" t="n">
-        <v>3.53</v>
+        <v>4.1</v>
       </c>
       <c r="P45" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="R45" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="U45" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X45" t="n">
-        <v>4.98</v>
+        <v>5.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Z45" t="n">
         <v>2.32</v>
@@ -6267,7 +6267,7 @@
         <v>1.67</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AD45" t="n">
         <v>2.44</v>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6354,34 +6354,34 @@
         <v>3.6</v>
       </c>
       <c r="O46" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
         <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
         <v>2.31</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X46" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Y46" t="n">
         <v>1.68</v>
@@ -6390,16 +6390,16 @@
         <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6483,34 +6483,34 @@
         <v>1.99</v>
       </c>
       <c r="O47" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="P47" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S47" t="n">
         <v>2.5</v>
       </c>
-      <c r="R47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T47" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
         <v>1.38</v>
       </c>
       <c r="X47" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="Y47" t="n">
         <v>2.25</v>
@@ -6519,16 +6519,16 @@
         <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6603,28 +6603,28 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O48" t="n">
-        <v>3.12</v>
+        <v>3.31</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S48" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
         <v>3.05</v>
@@ -6636,28 +6636,28 @@
         <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="X48" t="n">
         <v>2.78</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.35</v>
+        <v>4.28</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH48" t="n">
         <v>1.48</v>
@@ -6732,22 +6732,22 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O49" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="P49" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="R49" t="n">
         <v>1.41</v>
@@ -6771,19 +6771,19 @@
         <v>3.08</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD49" t="n">
         <v>1.96</v>
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH49" t="n">
         <v>1.56</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,34 +4410,34 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="N31" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
@@ -4446,13 +4446,13 @@
         <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>5.35</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AA31" t="n">
         <v>2.05</v>
@@ -4461,10 +4461,10 @@
         <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.09</v>
+        <v>2.76</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,34 +4539,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N32" t="n">
         <v>5.1</v>
       </c>
-      <c r="N32" t="n">
-        <v>6.7</v>
-      </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -4575,13 +4575,13 @@
         <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>6</v>
+        <v>5.35</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AA32" t="n">
         <v>2.05</v>
@@ -4590,10 +4590,10 @@
         <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.76</v>
+        <v>2.09</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="P36" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.8</v>
+        <v>1.89</v>
       </c>
       <c r="R36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="V36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.42</v>
+        <v>2.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>5.29</v>
+        <v>2.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O38" t="n">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T38" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W38" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z38" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z38" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AA38" t="n">
-        <v>2.06</v>
+        <v>5.29</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="P39" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
         <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X39" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>1.25</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O40" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
         <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>4.75</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M45" t="n">
         <v>3.61</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.77</v>
-      </c>
       <c r="N45" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="P45" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="U45" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X45" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD45" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.44</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.77</v>
+        <v>3.61</v>
       </c>
       <c r="M46" t="n">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O46" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R46" t="n">
         <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T46" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="U46" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X46" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Z46" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA46" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AB46" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,31 +4410,31 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="M31" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>6.7</v>
+        <v>3.67</v>
       </c>
       <c r="O31" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="P31" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
         <v>1.71</v>
@@ -4446,13 +4446,13 @@
         <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AA31" t="n">
         <v>2.05</v>
@@ -4461,10 +4461,10 @@
         <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.76</v>
+        <v>2.09</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="M32" t="n">
         <v>4.7</v>
       </c>
       <c r="N32" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.25</v>
+        <v>5.63</v>
       </c>
       <c r="R32" t="n">
         <v>1.21</v>
@@ -4563,7 +4563,7 @@
         <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
         <v>1.7</v>
@@ -4575,13 +4575,13 @@
         <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AA32" t="n">
         <v>2.05</v>
@@ -4590,10 +4590,10 @@
         <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.94</v>
+        <v>3.59</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>2.79</v>
       </c>
       <c r="N37" t="n">
-        <v>3.27</v>
+        <v>2.07</v>
       </c>
       <c r="O37" t="n">
-        <v>2.46</v>
+        <v>4.45</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.74</v>
+        <v>2.94</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="S37" t="n">
-        <v>4.1</v>
+        <v>2.23</v>
       </c>
       <c r="T37" t="n">
-        <v>2.04</v>
+        <v>3.54</v>
       </c>
       <c r="U37" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>6.15</v>
+        <v>2.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.45</v>
+        <v>2.62</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.76</v>
+        <v>1.44</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.13</v>
+        <v>5.29</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.36</v>
+        <v>2.14</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.77</v>
+        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,62 +5313,62 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.59</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2.07</v>
+        <v>3.13</v>
       </c>
       <c r="O38" t="n">
-        <v>4.45</v>
+        <v>2.47</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X38" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2.8</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O39" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="R39" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="U39" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W39" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.24</v>
+        <v>2.4</v>
       </c>
       <c r="R41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.42</v>
       </c>
-      <c r="S41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AC41" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5832,31 +5832,31 @@
         <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>4.03</v>
+        <v>4.4</v>
       </c>
       <c r="O42" t="n">
         <v>2.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.92</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
         <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U42" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V42" t="n">
         <v>1.05</v>
@@ -5865,19 +5865,19 @@
         <v>1.27</v>
       </c>
       <c r="X42" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AA42" t="n">
         <v>3.41</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC42" t="n">
         <v>1.8</v>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5958,37 +5958,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
         <v>2.15</v>
       </c>
       <c r="O43" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P43" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T43" t="n">
         <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
         <v>1.31</v>
@@ -5997,10 +5997,10 @@
         <v>3.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
         <v>3.08</v>
@@ -6009,7 +6009,7 @@
         <v>1.3</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD43" t="n">
         <v>2</v>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="M45" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T45" t="n">
         <v>2.31</v>
       </c>
       <c r="U45" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W45" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X45" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
         <v>2.55</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
         <v>1.95</v>
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="N46" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O46" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U46" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X46" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AC46" t="n">
         <v>1.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6483,31 +6483,31 @@
         <v>1.99</v>
       </c>
       <c r="O47" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q47" t="n">
         <v>2.64</v>
       </c>
       <c r="R47" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S47" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U47" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V47" t="n">
         <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X47" t="n">
         <v>3.03</v>
@@ -6519,16 +6519,16 @@
         <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB47" t="n">
         <v>1.25</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X48" t="n">
         <v>3.1</v>
       </c>
-      <c r="N48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.78</v>
-      </c>
       <c r="Y48" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.28</v>
+        <v>3.42</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>1.31</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y49" t="n">
         <v>2.2</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X49" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.09</v>
-      </c>
       <c r="Z49" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.42</v>
+        <v>4.28</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45960.40625</v>
+        <v>45960.39583333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45960.41666666666</v>
+        <v>45960.40625</v>
       </c>
     </row>
     <row r="7">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45960.46180555555</v>
+        <v>45960.45833333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45960.47916666666</v>
+        <v>45960.46180555555</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.47916666666</v>
       </c>
     </row>
     <row r="24">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="27">
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
         <v>3.52</v>
       </c>
       <c r="N27" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
         <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R27" t="n">
         <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="V27" t="n">
         <v>1.03</v>
@@ -3930,25 +3930,25 @@
         <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AA27" t="n">
         <v>2.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
         <v>1.48</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="30">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.63</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
         <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
         <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AA32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH32" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.73</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.57291666666</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="36">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O36" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.89</v>
+        <v>2.94</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T36" t="n">
-        <v>1.97</v>
+        <v>3.54</v>
       </c>
       <c r="U36" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>5.2</v>
+        <v>2.36</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.42</v>
+        <v>2.62</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.6</v>
+        <v>1.41</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.06</v>
+        <v>5.29</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.59</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.59</v>
+        <v>1.9</v>
       </c>
       <c r="M37" t="n">
-        <v>2.79</v>
+        <v>3.98</v>
       </c>
       <c r="N37" t="n">
-        <v>2.07</v>
+        <v>3.36</v>
       </c>
       <c r="O37" t="n">
-        <v>4.45</v>
+        <v>2.3</v>
       </c>
       <c r="P37" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="S37" t="n">
-        <v>2.23</v>
+        <v>3.98</v>
       </c>
       <c r="T37" t="n">
-        <v>3.54</v>
+        <v>2.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="V37" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>2.4</v>
+        <v>5.75</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.62</v>
+        <v>1.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="AA37" t="n">
-        <v>5.29</v>
+        <v>2.12</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.47</v>
+        <v>4.9</v>
       </c>
       <c r="P38" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.74</v>
+        <v>1.89</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U38" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X38" t="n">
-        <v>6.15</v>
+        <v>5.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.77</v>
+        <v>1.12</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5442,28 +5442,28 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
         <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R39" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="T39" t="n">
         <v>3.16</v>
@@ -5478,13 +5478,13 @@
         <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AA39" t="n">
         <v>3.68</v>
@@ -5574,58 +5574,58 @@
         <v>1.25</v>
       </c>
       <c r="M40" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O40" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="P40" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="T40" t="n">
         <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
         <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X40" t="n">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="Y40" t="n">
         <v>1.57</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5712,49 +5712,49 @@
         <v>4.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
         <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="Y41" t="n">
         <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AA41" t="n">
         <v>3.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
         <v>1.25</v>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="N42" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.15</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="O43" t="n">
-        <v>3.76</v>
+        <v>2.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="T43" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="V43" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="X43" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T44" t="n">
         <v>2.23</v>
       </c>
-      <c r="M44" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.47</v>
+        <v>2.34</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="O45" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="R45" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S45" t="n">
-        <v>3.42</v>
+        <v>2.59</v>
       </c>
       <c r="T45" t="n">
-        <v>2.31</v>
+        <v>3.22</v>
       </c>
       <c r="U45" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="V45" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X45" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,523 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Switzerland Super League</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Young Boys</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Pisa</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O47" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="n">
         <v>45960.69791666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>CS Marítimo</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>União de Leiria</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
-        <v>45960.71875</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Leixões</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
-        <v>45960.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45960.39583333334</v>
+        <v>45960.40625</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45960.40625</v>
+        <v>45960.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45960.45833333334</v>
+        <v>45960.46180555555</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45960.46180555555</v>
+        <v>45960.47916666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45960.47916666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="24">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="30">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>2.61</v>
@@ -4296,40 +4296,40 @@
         <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
         <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
         <v>2.82</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
         <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC30" t="n">
         <v>1.78</v>
@@ -4351,7 +4351,7 @@
         <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,31 +4539,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
         <v>1.71</v>
@@ -4575,25 +4575,25 @@
         <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
         <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="34">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.57291666666</v>
       </c>
     </row>
     <row r="36">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="P36" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.94</v>
+        <v>1.89</v>
       </c>
       <c r="R36" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.54</v>
+        <v>1.97</v>
       </c>
       <c r="U36" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="V36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>2.36</v>
+        <v>5.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>5.29</v>
+        <v>2.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.59</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O38" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="P38" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.89</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T38" t="n">
-        <v>1.97</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W38" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.42</v>
+        <v>2.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.06</v>
+        <v>5.29</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA39" t="n">
         <v>3.1</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.68</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="M40" t="n">
-        <v>5.55</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="S40" t="n">
-        <v>3.18</v>
+        <v>2.59</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="U40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>3.2</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O41" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="T41" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X41" t="n">
-        <v>3.58</v>
+        <v>4.55</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.23</v>
+        <v>3.03</v>
       </c>
       <c r="M42" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="M43" t="n">
         <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P43" t="n">
         <v>2.2</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Q43" t="n">
-        <v>4.2</v>
+        <v>5.02</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="T43" t="n">
-        <v>2.31</v>
+        <v>2.93</v>
       </c>
       <c r="U43" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="X43" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.55</v>
+        <v>3.37</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q44" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Z44" t="n">
-        <v>2.34</v>
+        <v>1.47</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,127 +6175,643 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="L47" t="n">
         <v>3.8</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M47" t="n">
         <v>3.25</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N47" t="n">
         <v>2.02</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O47" t="n">
         <v>4.2</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P47" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q47" t="n">
         <v>2.64</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R47" t="n">
         <v>1.49</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S47" t="n">
         <v>2.59</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T47" t="n">
         <v>3.22</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U47" t="n">
         <v>1.34</v>
       </c>
-      <c r="V45" t="n">
+      <c r="V47" t="n">
         <v>1.06</v>
       </c>
-      <c r="W45" t="n">
+      <c r="W47" t="n">
         <v>1.36</v>
       </c>
-      <c r="X45" t="n">
+      <c r="X47" t="n">
         <v>3.03</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Y47" t="n">
         <v>2.26</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="Z47" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AA47" t="n">
         <v>4</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AB47" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AC47" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AD47" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
         <v>1.35</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AH47" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" s="3" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
         <v>45960.69791666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CS Marítimo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>União de Leiria</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45960.71875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Leixões</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45960.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2613,7 +2613,7 @@
         <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
         <v>1.76</v>
@@ -2625,7 +2625,7 @@
         <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="T17" t="n">
         <v>4.1</v>
@@ -2643,7 +2643,7 @@
         <v>2.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Z17" t="n">
         <v>1.31</v>
@@ -2655,10 +2655,10 @@
         <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="M26" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
         <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,62 +4410,62 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.76</v>
       </c>
-      <c r="M31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AE31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>3.78</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,34 +4539,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="M32" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>3.67</v>
       </c>
       <c r="O32" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="P32" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.75</v>
+        <v>4.42</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
@@ -4581,19 +4581,19 @@
         <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA32" t="n">
         <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.89</v>
+        <v>3.79</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T36" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="U36" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
-        <v>5.2</v>
+        <v>6.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.28</v>
+        <v>3.02</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>3.59</v>
       </c>
       <c r="M37" t="n">
-        <v>3.98</v>
+        <v>2.79</v>
       </c>
       <c r="N37" t="n">
-        <v>3.36</v>
+        <v>2.07</v>
       </c>
       <c r="O37" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="R37" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="S37" t="n">
-        <v>3.98</v>
+        <v>2.21</v>
       </c>
       <c r="T37" t="n">
-        <v>2.11</v>
+        <v>3.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>5.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.44</v>
+        <v>2.62</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
+      <c r="AH37" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="R38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.54</v>
+        <v>1.97</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="V38" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="X38" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>5.29</v>
+        <v>2.06</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O39" t="n">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="P39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>9</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>3.58</v>
+        <v>5.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.25</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA40" t="n">
         <v>3.1</v>
       </c>
-      <c r="P40" t="n">
+      <c r="AB40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD40" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.25</v>
       </c>
-      <c r="M41" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="N41" t="n">
-        <v>12</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>8</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC41" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.03</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>4.85</v>
       </c>
       <c r="R42" t="n">
         <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="U42" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
         <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AB42" t="n">
         <v>1.29</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.84</v>
+        <v>3.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="O43" t="n">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.02</v>
+        <v>2.85</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
         <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.77</v>
+        <v>3.61</v>
       </c>
       <c r="M45" t="n">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O45" t="n">
-        <v>2.2</v>
+        <v>4.06</v>
       </c>
       <c r="P45" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA45" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AB45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC45" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AD45" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH45" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,62 +6345,62 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M46" t="n">
         <v>3.61</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.77</v>
-      </c>
       <c r="N46" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="P46" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="U46" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD46" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N47" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O47" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
         <v>1.36</v>
       </c>
       <c r="X47" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB47" t="n">
         <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6603,58 +6603,58 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.88</v>
       </c>
-      <c r="P48" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.06</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
         <v>1.33</v>
       </c>
       <c r="X48" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
         <v>1.92</v>
@@ -6673,7 +6673,7 @@
         <v>1.31</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6732,55 +6732,55 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P49" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="T49" t="n">
         <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
         <v>1.4</v>
       </c>
       <c r="X49" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC49" t="n">
         <v>1.85</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45960.39583333334</v>
+        <v>45960.40625</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45960.40625</v>
+        <v>45960.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45960.41666666666</v>
+        <v>45960.42708333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45960.42708333334</v>
+        <v>45960.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45960.4375</v>
+        <v>45960.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45960.45833333334</v>
+        <v>45960.46180555555</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45960.46180555555</v>
+        <v>45960.47916666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45960.47916666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="26">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="M31" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>3.67</v>
       </c>
       <c r="O31" t="n">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.75</v>
+        <v>4.42</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.78</v>
+        <v>2.05</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4935,13 +4935,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4950,37 +4950,37 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.57291666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5322,52 +5322,52 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="U38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.89</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC38" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T40" t="n">
         <v>3</v>
       </c>
-      <c r="T40" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U40" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.25</v>
       </c>
-      <c r="X40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y40" t="n">
+      <c r="AC40" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AD40" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N41" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5825,65 +5825,65 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.15</v>
+        <v>1.77</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N43" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="O43" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>4.85</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.23</v>
+        <v>3.61</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>3.77</v>
       </c>
       <c r="N44" t="n">
-        <v>3.05</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="M45" t="n">
-        <v>3.77</v>
+        <v>3.23</v>
       </c>
       <c r="N45" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R45" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y45" t="n">
         <v>2.25</v>
       </c>
-      <c r="U45" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X45" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.53</v>
-      </c>
       <c r="Z45" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.41</v>
+        <v>1.87</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="AH45" t="n">
         <v>1.25</v>
@@ -6295,523 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Switzerland Super League</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Lugano</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Luzern</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Pisa</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O47" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="n">
         <v>45960.69791666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>CS Marítimo</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>União de Leiria</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
-        <v>45960.71875</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Leixões</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
-        <v>45960.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.5</v>
       </c>
     </row>
     <row r="26">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>4.9</v>
       </c>
       <c r="M30" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>5.5</v>
+        <v>1.46</v>
       </c>
       <c r="O30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="31">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N31" t="n">
-        <v>3.67</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="P31" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.42</v>
+        <v>6.99</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="T31" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4935,13 +4935,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4950,37 +4950,37 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="36">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.57291666666</v>
       </c>
     </row>
     <row r="37">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.59</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>2.79</v>
+        <v>4.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.07</v>
+        <v>3.38</v>
       </c>
       <c r="O37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S37" t="n">
         <v>4</v>
       </c>
-      <c r="P37" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.21</v>
-      </c>
       <c r="T37" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="U37" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.11</v>
       </c>
-      <c r="W37" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X37" t="n">
-        <v>2.4</v>
+        <v>6.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.42</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.62</v>
+        <v>3.02</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O38" t="n">
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S38" t="n">
         <v>2.4</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
       <c r="T38" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="U38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.5</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X38" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="P39" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>1.89</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="U39" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
         <v>5.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>1.12</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5580,7 +5580,7 @@
         <v>2.88</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
         <v>2.1</v>
@@ -5589,19 +5589,19 @@
         <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W40" t="n">
         <v>1.35</v>
@@ -5619,13 +5619,13 @@
         <v>3.74</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC40" t="n">
         <v>1.89</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5825,65 +5825,65 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z43" t="n">
         <v>1.77</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA43" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>1.73</v>
+        <v>4.4</v>
       </c>
       <c r="O44" t="n">
-        <v>4.06</v>
+        <v>2.38</v>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="T44" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="U44" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W44" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X44" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>3.37</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,127 +6175,772 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45960.66666666666</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="L48" t="n">
         <v>3.86</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M48" t="n">
         <v>3.23</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N48" t="n">
         <v>1.99</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O48" t="n">
         <v>4</v>
       </c>
-      <c r="P45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q45" t="n">
+      <c r="P48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>2.5</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R48" t="n">
         <v>1.4</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S48" t="n">
         <v>2.75</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T48" t="n">
         <v>3</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U48" t="n">
         <v>1.36</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W45" t="n">
+      <c r="V48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W48" t="n">
         <v>1.36</v>
       </c>
-      <c r="X45" t="n">
+      <c r="X48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45960.69791666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CS Marítimo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>União de Leiria</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45960.71875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Leixões</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X50" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" s="3" t="n">
-        <v>45960.69791666666</v>
+      <c r="Y50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>45960.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3765,31 +3765,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O26" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
         <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
         <v>1.5</v>
@@ -3801,7 +3801,7 @@
         <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="Y26" t="n">
         <v>1.57</v>
@@ -3813,13 +3813,13 @@
         <v>2.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
         <v>1.53</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>5.83</v>
       </c>
       <c r="N32" t="n">
-        <v>3.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.42</v>
+        <v>6.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>5.75</v>
+        <v>6.43</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.06</v>
+        <v>3.77</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="M37" t="n">
-        <v>4.13</v>
+        <v>2.85</v>
       </c>
       <c r="N37" t="n">
-        <v>3.38</v>
+        <v>2.1</v>
       </c>
       <c r="O37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S37" t="n">
         <v>2.4</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4</v>
-      </c>
       <c r="T37" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="U37" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>6.25</v>
+        <v>2.38</v>
       </c>
       <c r="Y37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.59</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>4.23</v>
       </c>
       <c r="N38" t="n">
-        <v>2.07</v>
+        <v>3.68</v>
       </c>
       <c r="O38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S38" t="n">
         <v>4</v>
       </c>
-      <c r="P38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T38" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="U38" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="V38" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>2.4</v>
+        <v>6.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.44</v>
+        <v>2.98</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.15</v>
+        <v>1.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.67</v>
+        <v>2.98</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>3.94</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="T40" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="U40" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X40" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T41" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X41" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.25</v>
+        <v>4.83</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.2</v>
+        <v>2.46</v>
       </c>
       <c r="M42" t="n">
-        <v>6.1</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>11.4</v>
+        <v>2.88</v>
       </c>
       <c r="O42" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="T42" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W42" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="X42" t="n">
-        <v>5.2</v>
+        <v>3.11</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>3.74</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AH42" t="n">
-        <v>4.75</v>
+        <v>1.52</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5958,31 +5958,31 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="N43" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="O43" t="n">
-        <v>3.76</v>
+        <v>3.35</v>
       </c>
       <c r="P43" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.85</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.8</v>
       </c>
       <c r="U43" t="n">
         <v>1.4</v>
@@ -5994,13 +5994,13 @@
         <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AA43" t="n">
         <v>3.4</v>
@@ -6009,10 +6009,10 @@
         <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AD43" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH43" t="n">
         <v>1.3</v>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="M44" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
         <v>2.38</v>
@@ -6102,10 +6102,10 @@
         <v>2.09</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.2</v>
+        <v>4.02</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
         <v>2.9</v>
@@ -6120,16 +6120,16 @@
         <v>1.05</v>
       </c>
       <c r="W44" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X44" t="n">
         <v>3.3</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA44" t="n">
         <v>3.37</v>
@@ -6138,7 +6138,7 @@
         <v>1.29</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AD44" t="n">
         <v>1.88</v>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6225,19 +6225,19 @@
         <v>3.1</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -6246,31 +6246,31 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6732,19 +6732,19 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q49" t="n">
         <v>3.8</v>
@@ -6753,28 +6753,28 @@
         <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T49" t="n">
         <v>2.88</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
         <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X49" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
         <v>3.15</v>
@@ -6861,49 +6861,49 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O50" t="n">
         <v>3.2</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="R50" t="n">
         <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
         <v>3.1</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V50" t="n">
         <v>1.03</v>
       </c>
       <c r="W50" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="X50" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Y50" t="n">
         <v>2.2</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA50" t="n">
         <v>3.35</v>
@@ -6912,7 +6912,7 @@
         <v>1.19</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AD50" t="n">
         <v>1.85</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK50"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45960.5</v>
+        <v>45960.51041666666</v>
       </c>
     </row>
     <row r="26">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45960.51041666666</v>
+        <v>45960.52083333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45960.52083333334</v>
+        <v>45960.53125</v>
       </c>
     </row>
     <row r="29">
@@ -4152,19 +4152,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="O29" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
         <v>4.2</v>
@@ -4173,7 +4173,7 @@
         <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
         <v>2.82</v>
@@ -4194,7 +4194,7 @@
         <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
         <v>3.28</v>
@@ -4203,10 +4203,10 @@
         <v>1.27</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
         <v>1.7</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.9</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>5.83</v>
       </c>
       <c r="N30" t="n">
-        <v>1.46</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45960.53125</v>
+        <v>45960.54166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>8.880000000000001</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45960.54166666666</v>
+        <v>45960.5625</v>
       </c>
     </row>
     <row r="34">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.5625</v>
+        <v>45960.57291666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45960.57291666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>2.85</v>
+        <v>4.23</v>
       </c>
       <c r="N37" t="n">
-        <v>2.1</v>
+        <v>3.68</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.31</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.04</v>
+        <v>1.93</v>
       </c>
       <c r="R38" t="n">
         <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T38" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="U38" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>6.25</v>
+        <v>5.45</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
-        <v>4.9</v>
+        <v>2.94</v>
       </c>
       <c r="P39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S39" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
       <c r="T39" t="n">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>5.2</v>
+        <v>2.86</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.42</v>
+        <v>2.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.06</v>
+        <v>3.74</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O40" t="n">
-        <v>3.94</v>
+        <v>1.53</v>
       </c>
       <c r="P40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>9</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X40" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC40" t="n">
         <v>2.27</v>
       </c>
-      <c r="Q40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AD40" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.29</v>
+        <v>4.83</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1.53</v>
+        <v>3.94</v>
       </c>
       <c r="P41" t="n">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="T41" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U41" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>4.83</v>
+        <v>1.29</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
         <v>1.06</v>
       </c>
       <c r="W42" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X42" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="43">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,77 +5958,77 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.87</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="O43" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.92</v>
+        <v>4.02</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T43" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
         <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="Y43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y44" t="n">
         <v>2.38</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.99</v>
-      </c>
       <c r="Z44" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.37</v>
+        <v>4.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,62 +6216,62 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>3.89</v>
       </c>
       <c r="P45" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="R45" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S45" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V45" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="X45" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD45" t="n">
         <v>2.38</v>
       </c>
-      <c r="Z45" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="46">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.61</v>
+        <v>1.84</v>
       </c>
       <c r="M46" t="n">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>1.73</v>
+        <v>3.88</v>
       </c>
       <c r="O46" t="n">
-        <v>4.02</v>
+        <v>2.2</v>
       </c>
       <c r="P46" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.36</v>
+        <v>4.3</v>
       </c>
       <c r="R46" t="n">
         <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X46" t="n">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
         <v>2.35</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.77</v>
+        <v>3.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.61</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="O47" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S47" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X47" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.39</v>
+        <v>4.25</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.03</v>
+        <v>1.29</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.69791666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.86</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>1.99</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U48" t="n">
         <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="X48" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45960.69791666666</v>
+        <v>45960.71875</v>
       </c>
     </row>
     <row r="49">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
         <v>3.2</v>
       </c>
       <c r="N49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q49" t="n">
         <v>3.3</v>
       </c>
-      <c r="O49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R49" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S49" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T49" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
         <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X49" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Y49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC49" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD49" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,135 +6811,6 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45960.71875</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Leixões</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" s="3" t="n">
         <v>45960.71875</v>
       </c>
     </row>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.72</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>4.45</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>2.41</v>
       </c>
       <c r="P28" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.91</v>
+        <v>4.28</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.54</v>
+        <v>3.03</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.25</v>
+        <v>1.45</v>
       </c>
       <c r="O29" t="n">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>1.92</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>3.54</v>
       </c>
       <c r="T29" t="n">
-        <v>2.82</v>
+        <v>2.15</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X29" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>1.08</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,77 +5055,77 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>2.85</v>
+        <v>4.23</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>3.68</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="P36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X36" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.31</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.04</v>
+        <v>1.93</v>
       </c>
       <c r="R37" t="n">
         <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T37" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="U37" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>6.25</v>
+        <v>5.45</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.14</v>
+        <v>3.64</v>
       </c>
       <c r="U38" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>5.45</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z38" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z38" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>4.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>16</v>
       </c>
       <c r="O39" t="n">
-        <v>2.94</v>
+        <v>1.53</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.22</v>
+        <v>9</v>
       </c>
       <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.5</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="Z39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.08</v>
       </c>
-      <c r="W39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.52</v>
+        <v>4.5</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.21</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="O40" t="n">
-        <v>1.53</v>
+        <v>2.94</v>
       </c>
       <c r="P40" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="T40" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="X40" t="n">
-        <v>5</v>
+        <v>2.86</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.47</v>
+        <v>2.23</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.14</v>
+        <v>3.74</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.83</v>
+        <v>1.52</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5709,52 +5709,52 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P41" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
         <v>2.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
         <v>2.33</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>4.4</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>4.02</v>
       </c>
       <c r="R42" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T42" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
         <v>1.4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.25</v>
       </c>
-      <c r="X42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="O43" t="n">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="P43" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.02</v>
+        <v>2.9</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S43" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U43" t="n">
         <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X43" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>2.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AA44" t="n">
         <v>4.4</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.7</v>
+        <v>6.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.8</v>
+        <v>2.46</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45960.4375</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45960.4375</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45960.45833333334</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4032,34 +4032,34 @@
         <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
         <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="Y28" t="n">
         <v>1.95</v>
@@ -4068,16 +4068,16 @@
         <v>1.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4164,31 +4164,31 @@
         <v>5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R29" t="n">
         <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
         <v>1.47</v>
@@ -4203,10 +4203,10 @@
         <v>1.54</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4281,28 +4281,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="n">
-        <v>5.83</v>
+        <v>4.7</v>
       </c>
       <c r="N30" t="n">
-        <v>8.880000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P30" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="R30" t="n">
         <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
         <v>1.86</v>
@@ -4314,22 +4314,22 @@
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
         <v>1.62</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.77</v>
+        <v>3.36</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="M31" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="O31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.15</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA31" t="n">
         <v>2.05</v>
       </c>
-      <c r="U31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
         <v>1.53</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.57291666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="M36" t="n">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
         <v>3.68</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
         <v>1.22</v>
@@ -5079,34 +5079,34 @@
         <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="V36" t="n">
         <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AD36" t="n">
         <v>2.98</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P37" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
         <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="U37" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>1.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,78 +5313,78 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.59</v>
+        <v>2.46</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="R38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.53</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI38" t="n">
         <v>0</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5442,19 +5442,19 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="M39" t="n">
         <v>7</v>
       </c>
       <c r="N39" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O39" t="n">
         <v>1.53</v>
       </c>
       <c r="P39" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="Q39" t="n">
         <v>9</v>
@@ -5469,7 +5469,7 @@
         <v>2.23</v>
       </c>
       <c r="U39" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V39" t="n">
         <v>1.03</v>
@@ -5478,25 +5478,25 @@
         <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="Y39" t="n">
         <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="S40" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.36</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z40" t="n">
+      <c r="AC40" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA40" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Q41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X41" t="n">
         <v>2.5</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.6</v>
-      </c>
       <c r="Y41" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.66666666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="M42" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N42" t="n">
         <v>3.6</v>
       </c>
-      <c r="N42" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O42" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.02</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="X42" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.46</v>
+        <v>2.39</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="N43" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O43" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.01</v>
+        <v>2.48</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.625</v>
+        <v>45960.6875</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.26</v>
+        <v>3.86</v>
       </c>
       <c r="M44" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T44" t="n">
         <v>3</v>
       </c>
-      <c r="N44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="U44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AD44" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,11 +6154,11 @@
         </is>
       </c>
       <c r="AG44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH44" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH44" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
@@ -6166,652 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45960.66666666666</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Switzerland Super League</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Young Boys</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Switzerland Super League</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Lugano</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Luzern</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="3" t="n">
-        <v>45960.6875</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Pisa</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="n">
         <v>45960.69791666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>CS Marítimo</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>União de Leiria</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
-        <v>45960.71875</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Leixões</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
-        <v>45960.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK44"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45960.375</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.53</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.19</v>
+        <v>1.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45960.4375</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45960.4375</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45960.45833333334</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="U21" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,13 +3190,13 @@
         <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45960.47916666666</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N31" t="n">
-        <v>3.67</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.62</v>
+        <v>7.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="U31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.62</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD31" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.33</v>
+        <v>3.36</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>2.73</v>
@@ -4815,10 +4815,10 @@
         <v>3.04</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="T34" t="n">
         <v>2.14</v>
@@ -4830,22 +4830,22 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>5.53</v>
+        <v>5.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
         <v>1.38</v>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH34" t="n">
         <v>1.54</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45960.5625</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45960.58333333334</v>
+        <v>45960.57291666666</v>
       </c>
     </row>
     <row r="36">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.81</v>
+        <v>5.4</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3.68</v>
+        <v>1.48</v>
       </c>
       <c r="O36" t="n">
-        <v>2.18</v>
+        <v>5.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="R36" t="n">
         <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.06</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB36" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.98</v>
+        <v>2.25</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.04</v>
+        <v>1.13</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.4</v>
+        <v>1.81</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.48</v>
+        <v>3.68</v>
       </c>
       <c r="O37" t="n">
-        <v>5.25</v>
+        <v>2.18</v>
       </c>
       <c r="P37" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
         <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="V37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>2.98</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.13</v>
+        <v>2.04</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.46</v>
+        <v>3.59</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>2.88</v>
+        <v>2.07</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>3.64</v>
       </c>
       <c r="U38" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W38" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45960.60416666666</v>
+        <v>45960.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1.53</v>
+        <v>3.7</v>
       </c>
       <c r="P39" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.25</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X39" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.26</v>
+        <v>1.67</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>4</v>
+        <v>1.29</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O40" t="n">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="T40" t="n">
-        <v>2.59</v>
+        <v>2.23</v>
       </c>
       <c r="U40" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AA40" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.67</v>
+        <v>2.26</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O41" t="n">
         <v>3.1</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.95</v>
-      </c>
       <c r="P41" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V41" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="X41" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45960.66666666666</v>
+        <v>45960.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="Q42" t="n">
         <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
         <v>1.95</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.61</v>
+        <v>2.77</v>
       </c>
       <c r="M43" t="n">
-        <v>3.77</v>
+        <v>3.37</v>
       </c>
       <c r="N43" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="U43" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45960.6875</v>
+        <v>45960.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,127 +6046,772 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3" t="n">
+        <v>45960.66666666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>45960.6875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="L47" t="n">
         <v>3.86</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M47" t="n">
         <v>3.23</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N47" t="n">
         <v>1.99</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O47" t="n">
         <v>4</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P47" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q47" t="n">
         <v>2.5</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R47" t="n">
         <v>1.43</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S47" t="n">
         <v>2.65</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T47" t="n">
         <v>3</v>
       </c>
-      <c r="U44" t="n">
+      <c r="U47" t="n">
         <v>1.33</v>
       </c>
-      <c r="V44" t="n">
+      <c r="V47" t="n">
         <v>1.04</v>
       </c>
-      <c r="W44" t="n">
+      <c r="W47" t="n">
         <v>1.36</v>
       </c>
-      <c r="X44" t="n">
+      <c r="X47" t="n">
         <v>3</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y47" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="Z47" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AA47" t="n">
         <v>4.25</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AB47" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AC47" t="n">
         <v>1.98</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AD47" t="n">
         <v>1.87</v>
       </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
         <v>1.38</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AH47" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" s="3" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
         <v>45960.69791666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CS Marítimo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>União de Leiria</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45960.71875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Leixões</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45960.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="M2" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="P2" t="n">
         <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.62</v>
@@ -705,13 +705,13 @@
         <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AA2" t="n">
         <v>6.1</v>
@@ -723,7 +723,7 @@
         <v>2.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
         <v>1.42</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="M5" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>4.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>2.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.19</v>
+        <v>1.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>4.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45960.42708333334</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45960.4375</v>
@@ -1710,10 +1710,10 @@
         <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
         <v>6.05</v>
@@ -1722,13 +1722,13 @@
         <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
         <v>2.46</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>3.75</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45960.4375</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45960.46180555555</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
         <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" t="n">
         <v>2.1</v>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="N26" t="n">
         <v>2.14</v>
@@ -3777,49 +3777,49 @@
         <v>3.35</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
         <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
         <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45960.51041666666</v>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45960.52083333334</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>5.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q28" t="n">
-        <v>4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="AB28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.44</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45960.53125</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.2</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45960.53125</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="M31" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>3.67</v>
       </c>
       <c r="O31" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="P31" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.1</v>
+        <v>4.62</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.36</v>
+        <v>2.14</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45960.5625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.25</v>
+        <v>10.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45960.5625</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.4</v>
+        <v>3.59</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="O36" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P36" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="U36" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.14</v>
       </c>
-      <c r="X36" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z36" t="n">
+      <c r="AC36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI36" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.81</v>
+        <v>5.4</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3.68</v>
+        <v>1.48</v>
       </c>
       <c r="O37" t="n">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.06</v>
       </c>
-      <c r="U37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.98</v>
+        <v>2.1</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.04</v>
+        <v>1.13</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.59</v>
+        <v>1.87</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.07</v>
+        <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>2.18</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>3.64</v>
+        <v>2.06</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="V38" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="X38" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.59</v>
+        <v>1.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.95</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.13</v>
+        <v>1.74</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.23</v>
+        <v>1.35</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.31</v>
+        <v>2.04</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5442,34 +5442,34 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O39" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
         <v>2.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V39" t="n">
         <v>1</v>
@@ -5481,22 +5481,22 @@
         <v>3.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA39" t="n">
         <v>3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.18</v>
+        <v>2.46</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>11</v>
+        <v>2.88</v>
       </c>
       <c r="O40" t="n">
-        <v>1.53</v>
+        <v>2.94</v>
       </c>
       <c r="P40" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="S40" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="T40" t="n">
-        <v>2.23</v>
+        <v>3.31</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="X40" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.46</v>
+        <v>1.19</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.88</v>
+        <v>11</v>
       </c>
       <c r="O41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P41" t="n">
         <v>3.1</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.5</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AA41" t="n">
-        <v>3.76</v>
+        <v>2.25</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
         <v>3.55</v>
@@ -5841,13 +5841,13 @@
         <v>2.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R42" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
         <v>2.9</v>
@@ -5856,34 +5856,34 @@
         <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB42" t="n">
         <v>1.27</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45960.625</v>
@@ -5958,22 +5958,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="M43" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O43" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="P43" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
@@ -5982,16 +5982,16 @@
         <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="U43" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X43" t="n">
         <v>3.3</v>
@@ -6000,19 +6000,19 @@
         <v>1.87</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45960.625</v>
@@ -6087,22 +6087,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O44" t="n">
         <v>3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.95</v>
       </c>
       <c r="P44" t="n">
         <v>1.98</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R44" t="n">
         <v>1.49</v>
@@ -6111,10 +6111,10 @@
         <v>2.4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V44" t="n">
         <v>1.06</v>
@@ -6132,16 +6132,16 @@
         <v>1.47</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AB44" t="n">
         <v>1.14</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45960.66666666666</v>
@@ -6225,7 +6225,7 @@
         <v>1.73</v>
       </c>
       <c r="O45" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P45" t="n">
         <v>2.4</v>
@@ -6240,19 +6240,19 @@
         <v>3.42</v>
       </c>
       <c r="T45" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="U45" t="n">
         <v>1.59</v>
       </c>
       <c r="V45" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Y45" t="n">
         <v>1.58</v>
@@ -6270,7 +6270,7 @@
         <v>1.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,13 +6286,13 @@
         <v>1.27</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45960.6875</v>
@@ -6363,7 +6363,7 @@
         <v>4.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S46" t="n">
         <v>3.5</v>
@@ -6372,16 +6372,16 @@
         <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y46" t="n">
         <v>1.68</v>
@@ -6390,16 +6390,16 @@
         <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AB46" t="n">
         <v>1.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6418,10 +6418,10 @@
         <v>1.95</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45960.6875</v>
@@ -6483,7 +6483,7 @@
         <v>1.99</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="P47" t="n">
         <v>2.1</v>
@@ -6498,7 +6498,7 @@
         <v>2.65</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="U47" t="n">
         <v>1.33</v>
@@ -6510,7 +6510,7 @@
         <v>1.36</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y47" t="n">
         <v>2.25</v>
@@ -6519,16 +6519,16 @@
         <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AB47" t="n">
         <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6547,10 +6547,10 @@
         <v>1.3</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45960.69791666666</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="O48" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="P48" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y48" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y48" t="n">
+      <c r="Z48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z48" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD48" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45960.71875</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N49" t="n">
         <v>3.1</v>
       </c>
-      <c r="N49" t="n">
-        <v>2.62</v>
-      </c>
       <c r="O49" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T49" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X49" t="n">
-        <v>2.78</v>
+        <v>3.26</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.35</v>
+        <v>3.69</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45960.71875</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>3.36</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
         <v>3.4</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>3.98</v>
       </c>
       <c r="M9" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.68</v>
+        <v>4.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>2.49</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.25</v>
       </c>
-      <c r="X9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>1.21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45960.4375</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.05</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>3.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.24</v>
+        <v>5.1</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45960.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.75</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>6.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45960.4375</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.2</v>
+        <v>1.71</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45960.53125</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>5.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>1.38</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="T29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2.5</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.8</v>
+        <v>1.09</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45960.53125</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="M30" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="P30" t="n">
-        <v>2.98</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.3</v>
+        <v>4.62</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.81</v>
+        <v>2.38</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.36</v>
+        <v>2.15</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>3.67</v>
+        <v>9</v>
       </c>
       <c r="O31" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.62</v>
+        <v>7.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.15</v>
       </c>
-      <c r="X31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH31" t="n">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="O33" t="n">
-        <v>2.99</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.85</v>
+        <v>1.73</v>
       </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="U33" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.12</v>
       </c>
-      <c r="X33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.48</v>
+        <v>1</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45960.5625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45960.5625</v>
@@ -5055,31 +5055,31 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="M36" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9</v>
+        <v>4.82</v>
       </c>
       <c r="P36" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="R36" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="T36" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="U36" t="n">
         <v>1.25</v>
@@ -5088,28 +5088,28 @@
         <v>1.11</v>
       </c>
       <c r="W36" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X36" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.59</v>
+        <v>2.37</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AI36" t="n">
         <v>2.5</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.4</v>
+        <v>1.77</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
-        <v>5.5</v>
+        <v>2.26</v>
       </c>
       <c r="P37" t="n">
         <v>2.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="T37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>2.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.87</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3.6</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
-        <v>2.18</v>
+        <v>5.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.47</v>
+        <v>1.91</v>
       </c>
       <c r="R38" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="T38" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U38" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.12</v>
       </c>
-      <c r="X38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AI38" t="n">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.46</v>
+        <v>1.19</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>2.88</v>
+        <v>11</v>
       </c>
       <c r="O40" t="n">
-        <v>2.94</v>
+        <v>1.62</v>
       </c>
       <c r="P40" t="n">
-        <v>2.01</v>
+        <v>3.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.22</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="T40" t="n">
-        <v>3.31</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>2.9</v>
+        <v>5.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AA40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH40" t="n">
         <v>4</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AI40" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ40" t="n">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>2.96</v>
       </c>
       <c r="N41" t="n">
-        <v>11</v>
+        <v>2.84</v>
       </c>
       <c r="O41" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>3.68</v>
       </c>
       <c r="R41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.25</v>
       </c>
-      <c r="S41" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X41" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC41" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AH41" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AJ41" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45960.60416666666</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,22 +6216,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.61</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>1.73</v>
+        <v>3.8</v>
       </c>
       <c r="O45" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P45" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.45</v>
+        <v>3.85</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
@@ -6243,34 +6243,34 @@
         <v>2.31</v>
       </c>
       <c r="U45" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,16 +6283,16 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.57</v>
+        <v>2.37</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45960.6875</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.77</v>
+        <v>3.35</v>
       </c>
       <c r="M46" t="n">
-        <v>3.61</v>
+        <v>3.78</v>
       </c>
       <c r="N46" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O46" t="n">
         <v>3.6</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.2</v>
       </c>
       <c r="P46" t="n">
         <v>2.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T46" t="n">
         <v>2.3</v>
       </c>
       <c r="U46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y46" t="n">
         <v>1.53</v>
       </c>
-      <c r="V46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.68</v>
-      </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6415,13 +6415,13 @@
         <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.95</v>
+        <v>1.21</v>
       </c>
       <c r="AI46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45960.6875</v>
@@ -6474,31 +6474,31 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="M47" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N47" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="O47" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="R47" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S47" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
         <v>1.33</v>
@@ -6507,25 +6507,25 @@
         <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X47" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA47" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AB47" t="n">
         <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD47" t="n">
         <v>1.85</v>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
         <v>2.45</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.15</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.98</v>
+        <v>1.21</v>
       </c>
       <c r="O3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -837,10 +837,10 @@
         <v>5.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AA3" t="n">
         <v>2.1</v>
@@ -849,10 +849,10 @@
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="O8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.76</v>
+        <v>4.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" t="n">
         <v>1.74</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.98</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="P9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.49</v>
+        <v>6.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.21</v>
+        <v>2.46</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45960.4375</v>
@@ -1704,16 +1704,16 @@
         <v>1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
@@ -1734,16 +1734,16 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X10" t="n">
         <v>3.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
         <v>2.74</v>
@@ -1752,10 +1752,10 @@
         <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AI10" t="n">
         <v>1.19</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>3.98</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.16</v>
+        <v>2.49</v>
       </c>
       <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.35</v>
       </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.21</v>
       </c>
-      <c r="X11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45960.4375</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="N14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X14" t="n">
         <v>2.05</v>
       </c>
-      <c r="O14" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.76</v>
-      </c>
       <c r="Y14" t="n">
-        <v>2.26</v>
+        <v>3.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.78</v>
+        <v>3.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" t="n">
         <v>2.29</v>
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="R21" t="n">
         <v>1.19</v>
@@ -3144,7 +3144,7 @@
         <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="U21" t="n">
         <v>1.72</v>
@@ -3156,25 +3156,25 @@
         <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" t="n">
         <v>2.1</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3894,43 +3894,43 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="Y27" t="n">
         <v>2.2</v>
@@ -3939,16 +3939,16 @@
         <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" t="n">
         <v>2.08</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="O30" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.62</v>
+        <v>7.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="U30" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>4.75</v>
+        <v>6.65</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.65</v>
+        <v>3.96</v>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.3</v>
+        <v>3.07</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>3.94</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>6.65</v>
+        <v>2.88</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>2.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>9.449999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="P33" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>3.05</v>
+        <v>3.82</v>
       </c>
       <c r="T33" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AI33" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45960.5625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="O34" t="n">
-        <v>2.99</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.85</v>
+        <v>1.73</v>
       </c>
       <c r="R34" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="U34" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="V34" t="n">
         <v>1.02</v>
       </c>
       <c r="W34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.12</v>
       </c>
-      <c r="X34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45960.5625</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="O36" t="n">
-        <v>4.82</v>
+        <v>5.6</v>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="R36" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.31</v>
+        <v>3.38</v>
       </c>
       <c r="T36" t="n">
-        <v>3.38</v>
+        <v>2.15</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="V36" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>3.59</v>
       </c>
       <c r="M38" t="n">
-        <v>4.25</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="O38" t="n">
-        <v>5.6</v>
+        <v>4.86</v>
       </c>
       <c r="P38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI38" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ38" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,62 +5442,62 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="M39" t="n">
-        <v>3.48</v>
+        <v>3.03</v>
       </c>
       <c r="N39" t="n">
-        <v>1.99</v>
+        <v>2.95</v>
       </c>
       <c r="O39" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S39" t="n">
         <v>2.5</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
       <c r="T39" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.94</v>
       </c>
-      <c r="AA39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="M41" t="n">
-        <v>2.96</v>
+        <v>3.48</v>
       </c>
       <c r="N41" t="n">
-        <v>2.84</v>
+        <v>1.99</v>
       </c>
       <c r="O41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="P41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T41" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="U41" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="O42" t="n">
-        <v>2.45</v>
+        <v>3.56</v>
       </c>
       <c r="P42" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
         <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U42" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="X42" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Z42" t="n">
         <v>1.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45960.625</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O43" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="P43" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="T43" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U43" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45960.625</v>
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S44" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="T44" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="U44" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V44" t="n">
         <v>1.06</v>
       </c>
       <c r="W44" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="X44" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AA44" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AI44" t="n">
         <v>1.9</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,22 +6216,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="O45" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="P45" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.85</v>
+        <v>2.35</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
@@ -6240,37 +6240,37 @@
         <v>3.42</v>
       </c>
       <c r="T45" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y45" t="n">
         <v>1.57</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
         <v>2.35</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,13 +6286,13 @@
         <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AI45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45960.6875</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="M46" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="P46" t="n">
         <v>2.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="T46" t="n">
         <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X46" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
         <v>2.35</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6415,13 +6415,13 @@
         <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.21</v>
+        <v>1.95</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.57</v>
+        <v>2.37</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45960.6875</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O47" t="n">
         <v>4.5</v>
@@ -6489,13 +6489,13 @@
         <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R47" t="n">
         <v>1.51</v>
       </c>
       <c r="S47" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
@@ -6522,7 +6522,7 @@
         <v>3.86</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC47" t="n">
         <v>1.91</v>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI47" t="n">
         <v>2.45</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="P48" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q48" t="n">
         <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T48" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U48" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="X48" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45960.71875</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
         <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="P49" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R49" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S49" t="n">
         <v>2.65</v>
       </c>
       <c r="T49" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="X49" t="n">
-        <v>3.26</v>
+        <v>2.78</v>
       </c>
       <c r="Y49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC49" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AD49" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45960.71875</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
         <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.02</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="U2" t="n">
         <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Z2" t="n">
         <v>1.35</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
         <v>1.21</v>
       </c>
       <c r="O3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
         <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -849,10 +849,10 @@
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O5" t="n">
         <v>3.25</v>
       </c>
-      <c r="N5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.5</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>4.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.05</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AD7" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.13</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.5</v>
+        <v>2.87</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1452,25 +1452,25 @@
         <v>3.78</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
         <v>1.06</v>
@@ -1488,16 +1488,16 @@
         <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AB8" t="n">
         <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.16</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
         <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="AI9" t="n">
         <v>1.38</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>15</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>1.72</v>
+        <v>4.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="T10" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.21</v>
       </c>
-      <c r="X10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.72</v>
-      </c>
       <c r="AI10" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45960.4375</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.98</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.9</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AA11" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>4.54</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45960.4375</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4.37</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="T14" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.04</v>
+        <v>2.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3000,34 +3000,34 @@
         <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="P20" t="n">
         <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
         <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="Y20" t="n">
         <v>1.94</v>
@@ -3036,16 +3036,16 @@
         <v>1.76</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" t="n">
         <v>2.29</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
         <v>3.55</v>
@@ -3135,46 +3135,46 @@
         <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
         <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="T21" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI21" t="n">
         <v>2.1</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.14</v>
+        <v>2.37</v>
       </c>
       <c r="O26" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="P26" t="n">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="U26" t="n">
         <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" t="n">
         <v>2.1</v>
@@ -3903,34 +3903,34 @@
         <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.72</v>
+        <v>4.54</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.38</v>
+        <v>2.83</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="T27" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X27" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="Y27" t="n">
         <v>2.2</v>
@@ -3939,16 +3939,16 @@
         <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AB27" t="n">
         <v>1.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AI27" t="n">
         <v>2.08</v>
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.55</v>
       </c>
-      <c r="N28" t="n">
-        <v>3.8</v>
-      </c>
       <c r="O28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.3</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.66</v>
-      </c>
       <c r="U28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.4</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AI28" t="n">
         <v>1.65</v>
@@ -4152,58 +4152,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="O29" t="n">
         <v>5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V29" t="n">
         <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z29" t="n">
         <v>2.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD29" t="n">
         <v>2.2</v>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI29" t="n">
         <v>2.75</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.27</v>
+        <v>2.6</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.65</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>3.94</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>6.65</v>
+        <v>2.88</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="AA30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>2</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>2.5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N32" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="P32" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.62</v>
+        <v>7.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH32" t="n">
         <v>3.42</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI32" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="O33" t="n">
-        <v>3.21</v>
+        <v>9</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.62</v>
+        <v>1.74</v>
       </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>3.82</v>
+        <v>2.97</v>
       </c>
       <c r="T33" t="n">
-        <v>2.09</v>
+        <v>2.58</v>
       </c>
       <c r="U33" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.8</v>
+        <v>1.49</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45960.5625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>2.15</v>
       </c>
       <c r="M34" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>9.449999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="P34" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="R34" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AI34" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45960.5625</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>3.59</v>
       </c>
       <c r="M36" t="n">
-        <v>4.25</v>
+        <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="O36" t="n">
-        <v>5.6</v>
+        <v>4.45</v>
       </c>
       <c r="P36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S36" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>3.38</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.17</v>
       </c>
-      <c r="X36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI36" t="n">
         <v>2.5</v>
       </c>
-      <c r="AH36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.77</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="N37" t="n">
-        <v>3.8</v>
+        <v>1.44</v>
       </c>
       <c r="O37" t="n">
-        <v>2.26</v>
+        <v>5.65</v>
       </c>
       <c r="P37" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.18</v>
       </c>
-      <c r="S37" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X37" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>1.12</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.59</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.07</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
-        <v>4.86</v>
+        <v>2.2</v>
       </c>
       <c r="P38" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>2.33</v>
+        <v>4.2</v>
       </c>
       <c r="T38" t="n">
-        <v>3.38</v>
+        <v>2.05</v>
       </c>
       <c r="U38" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="V38" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.59</v>
+        <v>1.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.4</v>
+        <v>2.06</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.14</v>
+        <v>1.76</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.22</v>
+        <v>2.04</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>13</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.26</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="AB39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.04</v>
       </c>
-      <c r="W39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AH39" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.19</v>
+        <v>2.46</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>11</v>
+        <v>2.88</v>
       </c>
       <c r="O40" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="S40" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="X40" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AJ40" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5700,34 +5700,34 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O41" t="n">
         <v>3.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q41" t="n">
         <v>2.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U41" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
         <v>1</v>
@@ -5736,25 +5736,25 @@
         <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y41" t="n">
         <v>1.84</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AA41" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AB41" t="n">
         <v>1.41</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.31</v>
       </c>
       <c r="AI41" t="n">
         <v>2.29</v>
@@ -5841,31 +5841,31 @@
         <v>3.56</v>
       </c>
       <c r="P42" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R42" t="n">
         <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="T42" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X42" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="Y42" t="n">
         <v>1.93</v>
@@ -5877,13 +5877,13 @@
         <v>3.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC42" t="n">
         <v>1.67</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI42" t="n">
         <v>2.08</v>
@@ -5967,7 +5967,7 @@
         <v>4.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="P43" t="n">
         <v>2.23</v>
@@ -5979,22 +5979,22 @@
         <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
         <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
         <v>1.9</v>
@@ -6012,7 +6012,7 @@
         <v>1.86</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AI43" t="n">
         <v>1.66</v>
@@ -6096,28 +6096,28 @@
         <v>3.15</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Q44" t="n">
         <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="S44" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="T44" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="U44" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V44" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="W44" t="n">
         <v>1.57</v>
@@ -6132,16 +6132,16 @@
         <v>1.52</v>
       </c>
       <c r="AA44" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AI44" t="n">
         <v>1.9</v>
@@ -6216,37 +6216,37 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>3.77</v>
       </c>
       <c r="N45" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="O45" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P45" t="n">
         <v>2.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U45" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V45" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W45" t="n">
         <v>1.18</v>
@@ -6255,22 +6255,22 @@
         <v>4.75</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AI45" t="n">
         <v>2.5</v>
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="M46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N46" t="n">
         <v>3.6</v>
       </c>
-      <c r="N46" t="n">
-        <v>3.8</v>
-      </c>
       <c r="O46" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="P46" t="n">
         <v>2.45</v>
@@ -6363,16 +6363,16 @@
         <v>4.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
         <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
@@ -6384,19 +6384,19 @@
         <v>4.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AD46" t="n">
         <v>2.3</v>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
         <v>1.95</v>
@@ -6474,34 +6474,34 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N47" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="O47" t="n">
         <v>4.5</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R47" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
         <v>1.04</v>
@@ -6510,13 +6510,13 @@
         <v>1.42</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
         <v>3.86</v>
@@ -6528,7 +6528,7 @@
         <v>1.91</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
         <v>2.45</v>
@@ -6612,10 +6612,10 @@
         <v>2.85</v>
       </c>
       <c r="O48" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="P48" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
         <v>3.3</v>
@@ -6636,10 +6636,10 @@
         <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="X48" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="Y48" t="n">
         <v>2.03</v>
@@ -6648,7 +6648,7 @@
         <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AB48" t="n">
         <v>1.23</v>
@@ -6657,7 +6657,7 @@
         <v>1.88</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AI48" t="n">
         <v>1.8</v>
@@ -6741,19 +6741,19 @@
         <v>2.75</v>
       </c>
       <c r="O49" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="P49" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
       <c r="R49" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="T49" t="n">
         <v>3.1</v>
@@ -6765,10 +6765,10 @@
         <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X49" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Y49" t="n">
         <v>2.2</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI49" t="n">
         <v>1.99</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.53</v>
       </c>
-      <c r="M6" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.05</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.5</v>
+        <v>2.87</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
-        <v>5.29</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>4.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.28</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.62</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.61</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>14.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.91</v>
+        <v>4.54</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.24</v>
+        <v>5.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45960.4375</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4.29</v>
+        <v>2.38</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.26</v>
       </c>
-      <c r="X10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AH10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AI10" t="n">
-        <v>2.56</v>
+        <v>1.38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.62</v>
+        <v>3.24</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45960.4375</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>1.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>4.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.1</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.28</v>
       </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH11" t="n">
-        <v>4.54</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45960.4375</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45960.45833333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>5.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="O28" t="n">
-        <v>2.23</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.61</v>
+        <v>1.91</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="U28" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V28" t="n">
         <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AC28" t="n">
         <v>1.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.03</v>
+        <v>1.16</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45960.53125</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.2</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>5</v>
+        <v>2.23</v>
       </c>
       <c r="P29" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.91</v>
+        <v>4.61</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="T29" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="V29" t="n">
         <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X29" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
         <v>1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.16</v>
+        <v>2.03</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45960.53125</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>2.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>2</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N31" t="n">
-        <v>3.67</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="P31" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.62</v>
+        <v>7.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.62</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD31" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.15</v>
+        <v>3.42</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.58</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>6.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>2.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.81</v>
+        <v>1.61</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.17</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.42</v>
+        <v>1.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45960.54166666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.59</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>2.79</v>
+        <v>4.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="O36" t="n">
-        <v>4.45</v>
+        <v>5.65</v>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>3.38</v>
+        <v>2.29</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="V36" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.5</v>
       </c>
-      <c r="X36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.59</v>
-      </c>
       <c r="Z36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6</v>
+        <v>3.59</v>
       </c>
       <c r="M37" t="n">
-        <v>4.25</v>
+        <v>2.79</v>
       </c>
       <c r="N37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z37" t="n">
         <v>1.44</v>
       </c>
-      <c r="O37" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" t="n">
+      <c r="AA37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.25</v>
       </c>
-      <c r="S37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AI37" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.17</v>
+        <v>2.46</v>
       </c>
       <c r="M39" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>13</v>
+        <v>2.88</v>
       </c>
       <c r="O39" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="S39" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="X39" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AJ39" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U40" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="X40" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD40" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.6</v>
+        <v>1.17</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>13</v>
       </c>
       <c r="O41" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="P41" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="T41" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
-        <v>3.42</v>
+        <v>5.75</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.25</v>
+        <v>4.75</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.29</v>
+        <v>1.22</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.68</v>
+        <v>4.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45960.60416666666</v>

--- a/jogos_2025-10-30.xlsx
+++ b/jogos_2025-10-30.xlsx
@@ -665,59 +665,59 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
         <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="T2" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="U2" t="n">
         <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
         <v>2.3</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AI2" t="n">
         <v>2.04</v>
@@ -781,100 +781,100 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
         <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.55</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '75']</t>
         </is>
       </c>
       <c r="AG3" t="n">
         <v>1.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45960.39583333334</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -933,7 +933,7 @@
         <v>2.78</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.5</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AA5" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1119,20 +1119,20 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '90+3']</t>
         </is>
       </c>
       <c r="AG5" t="n">
         <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>5.29</v>
+        <v>2.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>4.34</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.46</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['45+2', '77', '82']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['10', '53']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.62</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.61</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.53</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="X7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['49', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.62</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45960.41666666666</v>
@@ -1426,48 +1426,48 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
         <v>1.25</v>
@@ -1476,44 +1476,44 @@
         <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AD8" t="n">
         <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AI8" t="n">
         <v>1.74</v>
@@ -1555,51 +1555,51 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
         <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.1</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
         <v>1.05</v>
@@ -1608,41 +1608,41 @@
         <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
         <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.33</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>['41', '90']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="AI9" t="n">
         <v>1.19</v>
@@ -1684,54 +1684,54 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T10" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="U10" t="n">
         <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
         <v>1.25</v>
@@ -1740,10 +1740,10 @@
         <v>3.28</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AA10" t="n">
         <v>3.08</v>
@@ -1752,26 +1752,26 @@
         <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '51', '76']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AI10" t="n">
         <v>1.38</v>
@@ -1826,26 +1826,26 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>3.18</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="O11" t="n">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="R11" t="n">
         <v>1.39</v>
@@ -1869,38 +1869,38 @@
         <v>3.22</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" t="n">
         <v>2.56</v>
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,87 +2578,87 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2667,20 +2667,20 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '90+5']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45960.45833333334</v>
@@ -2977,17 +2977,17 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3000,16 +3000,16 @@
         <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
         <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
         <v>2.8</v>
@@ -3018,16 +3018,16 @@
         <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Y20" t="n">
         <v>1.94</v>
@@ -3036,16 +3036,16 @@
         <v>1.76</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '48', '90']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" t="n">
         <v>2.29</v>
@@ -3103,20 +3103,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3147,16 +3147,16 @@
         <v>2.02</v>
       </c>
       <c r="U21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="Y21" t="n">
         <v>1.58</v>
@@ -3174,23 +3174,23 @@
         <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '55', '90+3']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG21" t="n">
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
         <v>2.1</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3632,87 +3632,87 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45960.51041666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45960.51041666666</v>
@@ -3877,48 +3877,48 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="M27" t="n">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>4.54</v>
+        <v>4.1</v>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="R27" t="n">
         <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
         <v>1.3</v>
@@ -3927,44 +3927,44 @@
         <v>1.07</v>
       </c>
       <c r="W27" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X27" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '90+4']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AI27" t="n">
         <v>2.08</v>
@@ -4009,36 +4009,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="N28" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="P28" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -4047,10 +4047,10 @@
         <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
         <v>1.03</v>
@@ -4059,25 +4059,25 @@
         <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" t="n">
         <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4086,14 +4086,14 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '60', '81']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AI28" t="n">
         <v>2.75</v>
@@ -4135,94 +4135,94 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>4.61</v>
       </c>
       <c r="O29" t="n">
         <v>2.23</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.61</v>
+        <v>4.35</v>
       </c>
       <c r="R29" t="n">
         <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="U29" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X29" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['36', '61']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.03</v>
       </c>
       <c r="AI29" t="n">
         <v>1.65</v>
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S30" t="n">
         <v>4</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.2</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X30" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="P31" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.1</v>
+        <v>5.44</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
         <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '45+2']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '83']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.42</v>
+        <v>2.62</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45960.54166666666</v>
@@ -4535,65 +4535,65 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
         <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
         <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI32" t="n">
         <v>2.1</v>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -4664,81 +4664,81 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>10.5</v>
+        <v>14.9</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="O33" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="V33" t="n">
         <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X33" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB33" t="n">
         <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78', '90+9']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AI33" t="n">
         <v>4</v>
@@ -4780,48 +4780,48 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="U34" t="n">
         <v>1.71</v>
@@ -4830,44 +4830,44 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AD34" t="n">
         <v>2.8</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '45+10', '52', '55', '74']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI34" t="n">
         <v>1.91</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="M36" t="n">
-        <v>4.25</v>
+        <v>2.93</v>
       </c>
       <c r="N36" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
-        <v>5.65</v>
+        <v>4.24</v>
       </c>
       <c r="P36" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="R36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.25</v>
       </c>
-      <c r="S36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.57</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W36" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5148,119 +5148,119 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.59</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>2.79</v>
+        <v>4.33</v>
       </c>
       <c r="N37" t="n">
-        <v>2.07</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
-        <v>4.45</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="T37" t="n">
-        <v>3.38</v>
+        <v>1.91</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="V37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.59</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.44</v>
+        <v>3.54</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '50', '65']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5277,119 +5277,119 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>1.44</v>
       </c>
       <c r="O38" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="P38" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="AA38" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2.06</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '77', '90+2']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '45+3']</t>
         </is>
       </c>
       <c r="AG38" t="n">
         <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.04</v>
+        <v>1.13</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45960.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="O39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA39" t="n">
         <v>3.1</v>
       </c>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4</v>
-      </c>
       <c r="AB39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['5', '82']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['8', '32', '66']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5545,19 +5545,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -5567,87 +5567,87 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.6</v>
+        <v>1.14</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>7.5</v>
       </c>
       <c r="N40" t="n">
-        <v>1.95</v>
+        <v>11.7</v>
       </c>
       <c r="O40" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="P40" t="n">
-        <v>2.12</v>
+        <v>2.86</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.5</v>
+        <v>8.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="T40" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.4</v>
       </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.84</v>
-      </c>
       <c r="Z40" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+11']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>4.19</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.29</v>
+        <v>1.22</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.68</v>
+        <v>4.5</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,19 +5674,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -5696,87 +5696,87 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>13</v>
+        <v>2.82</v>
       </c>
       <c r="O41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R41" t="n">
         <v>1.5</v>
       </c>
-      <c r="P41" t="n">
+      <c r="S41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T41" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U41" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W41" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="X41" t="n">
-        <v>5.75</v>
+        <v>2.74</v>
       </c>
       <c r="Y41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['54', '65']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AI41" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AJ41" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45960.60416666666</v>
@@ -5815,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -5825,65 +5825,65 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="O42" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="P42" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="R42" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U42" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X42" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5892,14 +5892,14 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AI42" t="n">
         <v>2.08</v>
@@ -5941,39 +5941,39 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="O43" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="P43" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
@@ -5982,25 +5982,25 @@
         <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U43" t="n">
         <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA43" t="n">
         <v>3.14</v>
@@ -6009,26 +6009,26 @@
         <v>1.27</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '45+3']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AI43" t="n">
         <v>1.66</v>
@@ -6070,94 +6070,94 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="M44" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
         <v>2.93</v>
       </c>
       <c r="P44" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="S44" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T44" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U44" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.13</v>
       </c>
-      <c r="W44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AC44" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '51']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG44" t="n">
         <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI44" t="n">
         <v>1.9</v>
@@ -6199,94 +6199,94 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.77</v>
+        <v>3.63</v>
       </c>
       <c r="N45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="Y45" t="n">
         <v>1.73</v>
       </c>
-      <c r="O45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Z45" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '25', '74']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '67', '89']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI45" t="n">
         <v>2.5</v>
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -6341,26 +6341,26 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O46" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P46" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
         <v>1.25</v>
@@ -6372,50 +6372,50 @@
         <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X46" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
+          <t>['52', '63']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AI46" t="n">
         <v>1.57</v>
@@ -6470,81 +6470,81 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="O47" t="n">
         <v>4.5</v>
       </c>
       <c r="P47" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
         <v>1.4</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH47" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI47" t="n">
         <v>2.45</v>
@@ -6586,39 +6586,39 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="M48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N48" t="n">
         <v>3.15</v>
       </c>
-      <c r="N48" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O48" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="R48" t="n">
         <v>1.36</v>
@@ -6627,22 +6627,22 @@
         <v>2.8</v>
       </c>
       <c r="T48" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U48" t="n">
         <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X48" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="Z48" t="n">
         <v>1.7</v>
@@ -6651,26 +6651,26 @@
         <v>3.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72', '76', '88']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH48" t="n">
         <v>1.72</v>
@@ -6715,39 +6715,39 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="O49" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P49" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.61</v>
+        <v>3.19</v>
       </c>
       <c r="R49" t="n">
         <v>1.44</v>
@@ -6762,47 +6762,47 @@
         <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W49" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="X49" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '25', '50', '66', '90+4']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AI49" t="n">
         <v>1.99</v>
